--- a/314e-ig/output/StructureDefinition-contract-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-contract-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-11T14:17:09+05:30</t>
+    <t>2026-06-18T13:36:33+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-contract-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-contract-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T13:36:33+05:30</t>
+    <t>2026-06-18T14:15:04+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-contract-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-contract-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T14:15:04+05:30</t>
+    <t>2026-06-18T16:14:31+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-contract-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-contract-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T16:14:31+05:30</t>
+    <t>2026-06-24T16:34:23+05:30</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -752,7 +752,7 @@
     <t>Contract.authority</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/organization-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -775,7 +775,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Location) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/location-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -848,7 +848,7 @@
     <t>Contract.author</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient|Practitioner|PractitionerRole|Organization) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/patient-314e|http://314e.com/fhir/StructureDefinition/practitioner-314e|http://314e.com/fhir/StructureDefinition/practitionerrole-314e|http://314e.com/fhir/StructureDefinition/organization-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -1138,7 +1138,7 @@
     <t>Contract.term.topic[x]</t>
   </si>
   <si>
-    <t>CodeableConcept {http://314e.com/fhir/ig/StructureDefinition/codeableconcept-314e}
+    <t>CodeableConcept(Resource) {http://314e.com/fhir/ig/StructureDefinition/codeableconcept-314e}
 Reference(Resource) {http://314e.com/fhir/StructureDefinition/reference-314e}</t>
   </si>
   <si>
@@ -1998,7 +1998,7 @@
     <t>Contract.term.action.subject.reference</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient|RelatedPerson|Practitioner|PractitionerRole|Device|Group|Organization) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/patient-314e|http://314e.com/fhir/StructureDefinition/relatedperson-314e|http://314e.com/fhir/StructureDefinition/practitioner-314e|http://314e.com/fhir/StructureDefinition/practitionerrole-314e|http://314e.com/fhir/StructureDefinition/device-314e|http://314e.com/fhir/StructureDefinition/group-314e|http://314e.com/fhir/StructureDefinition/organization-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -2079,7 +2079,7 @@
     <t>Contract.term.action.context</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Encounter|EpisodeOfCare) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/encounter-314e|http://314e.com/fhir/StructureDefinition/episodeofcare-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -2153,7 +2153,7 @@
     <t>Contract.term.action.performer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(RelatedPerson|Patient|Practitioner|PractitionerRole|CareTeam|Device|Substance|Organization|Location) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/relatedperson-314e|http://314e.com/fhir/StructureDefinition/patient-314e|http://314e.com/fhir/StructureDefinition/practitioner-314e|http://314e.com/fhir/StructureDefinition/practitionerrole-314e|http://314e.com/fhir/StructureDefinition/careteam-314e|http://314e.com/fhir/StructureDefinition/device-314e|http://314e.com/fhir/StructureDefinition/substance-314e|http://314e.com/fhir/StructureDefinition/organization-314e|http://314e.com/fhir/StructureDefinition/location-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -2181,7 +2181,7 @@
     <t>Contract.term.action.reasonReference</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Condition|Observation|DiagnosticReport|DocumentReference|Questionnaire|QuestionnaireResponse) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/condition-314e|http://314e.com/fhir/StructureDefinition/condition-diagnosis-314e|http://314e.com/fhir/StructureDefinition/condition-problem-healthconcern-314e|http://314e.com/fhir/StructureDefinition/observation-314e|http://314e.com/fhir/StructureDefinition/observation-lab-general-314e|http://314e.com/fhir/StructureDefinition/observation-microbiology-314e|http://314e.com/fhir/StructureDefinition/observation-microorganism-314e|http://314e.com/fhir/StructureDefinition/observation-antimicrobial-susceptibility-314e|http://314e.com/fhir/StructureDefinition/diagnosticreport-314e|http://314e.com/fhir/StructureDefinition/diagnosticreport-lab-314e|http://314e.com/fhir/StructureDefinition/diagnosticreport-notereport-314e|http://314e.com/fhir/StructureDefinition/documentreference-314e|Questionnaire|http://314e.com/fhir/StructureDefinition/questionnaireresponse-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -2309,7 +2309,7 @@
     <t>Contract.signer.party</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization|Patient|Practitioner|PractitionerRole|RelatedPerson) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/organization-314e|http://314e.com/fhir/StructureDefinition/patient-314e|http://314e.com/fhir/StructureDefinition/practitioner-314e|http://314e.com/fhir/StructureDefinition/practitionerrole-314e|http://314e.com/fhir/StructureDefinition/relatedperson-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -2369,7 +2369,7 @@
     <t>Contract.friendly.content[x]</t>
   </si>
   <si>
-    <t>Attachment {http://314e.com/fhir/StructureDefinition/attachment-314e}
+    <t>Attachment(Composition|http://314e.com/fhir/StructureDefinition/documentreference-314e|http://314e.com/fhir/StructureDefinition/questionnaireresponse-314e) {http://314e.com/fhir/StructureDefinition/attachment-314e}
 Reference(Composition|DocumentReference|QuestionnaireResponse) {http://314e.com/fhir/StructureDefinition/reference-314e}</t>
   </si>
   <si>
@@ -2433,7 +2433,7 @@
     <t>Contract.rule.content[x]</t>
   </si>
   <si>
-    <t>Attachment {http://314e.com/fhir/StructureDefinition/attachment-314e}
+    <t>Attachment(http://314e.com/fhir/StructureDefinition/documentreference-314e) {http://314e.com/fhir/StructureDefinition/attachment-314e}
 Reference(DocumentReference) {http://314e.com/fhir/StructureDefinition/reference-314e}</t>
   </si>
   <si>
@@ -2788,7 +2788,7 @@
     <col min="8" max="8" width="13.1171875" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="10.75390625" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="144.171875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="255.0" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/314e-ig/output/StructureDefinition-contract-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-contract-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-24T16:34:23+05:30</t>
+    <t>2026-06-29T17:18:47+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-contract-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-contract-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T17:18:47+05:30</t>
+    <t>2026-07-01T18:18:44+05:30</t>
   </si>
   <si>
     <t>Publisher</t>
